--- a/docentes/Domínguez Burgos Marioscar - Estadisticos 20212.xlsx
+++ b/docentes/Domínguez Burgos Marioscar - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="58">
   <si>
     <t>Mat</t>
   </si>
@@ -79,139 +79,118 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>ARRIETA</t>
-  </si>
-  <si>
-    <t>CERVANTES</t>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>MANZANET</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>XOLIO</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>GALVEZ</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
   </si>
   <si>
     <t>CORTES</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GALVEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MANUEL</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>PATIÑO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>NAVA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>AULIS</t>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>LINARES</t>
+  </si>
+  <si>
+    <t>ROQUE</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
   </si>
   <si>
     <t>ALTAMIRANO</t>
   </si>
   <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>JESUS ALBERTO</t>
-  </si>
-  <si>
-    <t>GIOVANNI</t>
-  </si>
-  <si>
-    <t>SAUL ESTEBAN</t>
-  </si>
-  <si>
-    <t>ALDO</t>
+    <t>EUSEBIO</t>
+  </si>
+  <si>
+    <t>JONATHAN</t>
+  </si>
+  <si>
+    <t>ALEXIS ARMANDO</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>ARTURO</t>
+  </si>
+  <si>
+    <t>ESDRAS ALAN</t>
+  </si>
+  <si>
+    <t>JADE EMILY</t>
+  </si>
+  <si>
+    <t>ADAN</t>
+  </si>
+  <si>
+    <t>HERSON ELIAS</t>
+  </si>
+  <si>
+    <t>ANDRES</t>
+  </si>
+  <si>
+    <t>CONCEPCION</t>
+  </si>
+  <si>
+    <t>ASHLEY ZURELY</t>
   </si>
   <si>
     <t>ADRIAN</t>
   </si>
   <si>
-    <t>ABRAHAM</t>
-  </si>
-  <si>
-    <t>ARELY</t>
-  </si>
-  <si>
     <t>JESUS MANUEL</t>
-  </si>
-  <si>
-    <t>RUBEN</t>
-  </si>
-  <si>
-    <t>LUZ ABRIL</t>
-  </si>
-  <si>
-    <t>VICTOR YAHIR</t>
-  </si>
-  <si>
-    <t>CRISTOPHER ENRIQUE</t>
-  </si>
-  <si>
-    <t>CARLOS FERNANDO</t>
-  </si>
-  <si>
-    <t>CIELO IVETTE</t>
-  </si>
-  <si>
-    <t>GWINETH</t>
-  </si>
-  <si>
-    <t>YOSEF OMAR</t>
-  </si>
-  <si>
-    <t>EDGAR</t>
   </si>
 </sst>
 </file>
@@ -664,16 +643,19 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>59.38</v>
+      </c>
+      <c r="H4">
+        <v>7.2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -827,7 +809,7 @@
         <v>32</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -984,16 +966,19 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>59.38</v>
+      </c>
+      <c r="H4">
+        <v>7.2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1055,7 +1040,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1087,22 +1072,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920307</v>
+        <v>19330051920045</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1110,22 +1095,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920309</v>
+        <v>19330051920057</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1133,22 +1118,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920316</v>
+        <v>19330051920058</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1156,22 +1141,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920318</v>
+        <v>19330051920068</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1179,22 +1164,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920319</v>
+        <v>19330051920075</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1202,22 +1187,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920323</v>
+        <v>19330051920273</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1225,22 +1210,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920441</v>
+        <v>19330051920286</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1248,16 +1233,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920325</v>
+        <v>19330051920352</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1271,19 +1256,19 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920332</v>
+        <v>19330051920353</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
         <v>12</v>
@@ -1294,85 +1279,85 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920331</v>
+        <v>19330051920278</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920333</v>
+        <v>19330051920284</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920337</v>
+        <v>19330051920443</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D13" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920341</v>
+        <v>19330051920323</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="D14" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1381,21 +1366,21 @@
         <v>12</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051920344</v>
+        <v>19330051920332</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D15" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1404,99 +1389,7 @@
         <v>12</v>
       </c>
       <c r="G15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>19330051920440</v>
-      </c>
-      <c r="B16" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" t="s">
-        <v>44</v>
-      </c>
-      <c r="D16" t="s">
-        <v>61</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>19330051920345</v>
-      </c>
-      <c r="B17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" t="s">
-        <v>28</v>
-      </c>
-      <c r="D17" t="s">
-        <v>62</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>19330051920346</v>
-      </c>
-      <c r="B18" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" t="s">
-        <v>45</v>
-      </c>
-      <c r="D18" t="s">
-        <v>63</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>19330051920351</v>
-      </c>
-      <c r="B19" t="s">
-        <v>34</v>
-      </c>
-      <c r="C19" t="s">
-        <v>46</v>
-      </c>
-      <c r="D19" t="s">
-        <v>64</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Domínguez Burgos Marioscar - Estadisticos 20212.xlsx
+++ b/docentes/Domínguez Burgos Marioscar - Estadisticos 20212.xlsx
@@ -100,24 +100,24 @@
     <t>MANZANET</t>
   </si>
   <si>
+    <t>XOLIO</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>GALVEZ</t>
+  </si>
+  <si>
     <t>VILLA</t>
   </si>
   <si>
-    <t>XOLIO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>GALVEZ</t>
-  </si>
-  <si>
     <t>DE LOS SANTOS</t>
   </si>
   <si>
@@ -172,25 +172,25 @@
     <t>JADE EMILY</t>
   </si>
   <si>
+    <t>HERSON ELIAS</t>
+  </si>
+  <si>
+    <t>ANDRES</t>
+  </si>
+  <si>
+    <t>CONCEPCION</t>
+  </si>
+  <si>
+    <t>ASHLEY ZURELY</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>JESUS MANUEL</t>
+  </si>
+  <si>
     <t>ADAN</t>
-  </si>
-  <si>
-    <t>HERSON ELIAS</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>CONCEPCION</t>
-  </si>
-  <si>
-    <t>ASHLEY ZURELY</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>JESUS MANUEL</t>
   </si>
 </sst>
 </file>
@@ -1233,19 +1233,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920352</v>
+        <v>19330051920353</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
         <v>51</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
         <v>12</v>
@@ -1256,13 +1256,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920353</v>
+        <v>19330051920278</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
         <v>52</v>
@@ -1271,21 +1271,21 @@
         <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920278</v>
+        <v>19330051920284</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
         <v>53</v>
@@ -1302,13 +1302,13 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920284</v>
+        <v>19330051920443</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D12" t="s">
         <v>54</v>
@@ -1325,22 +1325,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920443</v>
+        <v>19330051920323</v>
       </c>
       <c r="B13" t="s">
         <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D13" t="s">
         <v>55</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1348,13 +1348,13 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920323</v>
+        <v>19330051920332</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="D14" t="s">
         <v>56</v>
@@ -1371,13 +1371,13 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051920332</v>
+        <v>19330051920352</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="D15" t="s">
         <v>57</v>

--- a/docentes/Domínguez Burgos Marioscar - Estadisticos 20212.xlsx
+++ b/docentes/Domínguez Burgos Marioscar - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="72">
   <si>
     <t>Mat</t>
   </si>
@@ -85,78 +85,126 @@
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>MANZANET</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>MANZANET</t>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>GALVEZ</t>
+  </si>
+  <si>
+    <t>VILLA</t>
   </si>
   <si>
     <t>XOLIO</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>GALVEZ</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
     <t>DE LOS SANTOS</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>MONTERO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
     <t>PACHECO</t>
   </si>
   <si>
     <t>CORTES</t>
   </si>
   <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
+    <t>LINARES</t>
+  </si>
+  <si>
+    <t>ROQUE</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>ALTAMIRANO</t>
   </si>
   <si>
     <t>RAMOS</t>
   </si>
   <si>
-    <t>LINARES</t>
-  </si>
-  <si>
-    <t>ROQUE</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>ALTAMIRANO</t>
-  </si>
-  <si>
     <t>EUSEBIO</t>
   </si>
   <si>
     <t>JONATHAN</t>
   </si>
   <si>
+    <t>ISAAC ALESSANDRO</t>
+  </si>
+  <si>
+    <t>ALEXIS YAIR</t>
+  </si>
+  <si>
+    <t>IVAN</t>
+  </si>
+  <si>
+    <t>JOSUE YAMIN</t>
+  </si>
+  <si>
+    <t>ESDRAS ALAN</t>
+  </si>
+  <si>
+    <t>JADE EMILY</t>
+  </si>
+  <si>
+    <t>CARLO HUMBERTO</t>
+  </si>
+  <si>
     <t>ALEXIS ARMANDO</t>
   </si>
   <si>
@@ -166,31 +214,25 @@
     <t>ARTURO</t>
   </si>
   <si>
-    <t>ESDRAS ALAN</t>
-  </si>
-  <si>
-    <t>JADE EMILY</t>
+    <t>ANDRES</t>
+  </si>
+  <si>
+    <t>CONCEPCION</t>
+  </si>
+  <si>
+    <t>ASHLEY ZURELY</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>JESUS MANUEL</t>
+  </si>
+  <si>
+    <t>ADAN</t>
   </si>
   <si>
     <t>HERSON ELIAS</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>CONCEPCION</t>
-  </si>
-  <si>
-    <t>ASHLEY ZURELY</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>JESUS MANUEL</t>
-  </si>
-  <si>
-    <t>ADAN</t>
   </si>
 </sst>
 </file>
@@ -1040,7 +1082,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1078,10 +1120,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1101,10 +1143,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1118,16 +1160,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920058</v>
+        <v>18330051920022</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1141,16 +1183,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920068</v>
+        <v>19330051920067</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1164,16 +1206,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920075</v>
+        <v>19330051920074</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1187,22 +1229,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920273</v>
+        <v>18330051920078</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1210,16 +1252,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920286</v>
+        <v>19330051920273</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1233,22 +1275,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920353</v>
+        <v>19330051920286</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1256,68 +1298,68 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920278</v>
+        <v>19330051920308</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920284</v>
+        <v>19330051920308</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920443</v>
+        <v>19330051920058</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1325,22 +1367,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920323</v>
+        <v>19330051920068</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1348,22 +1390,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920332</v>
+        <v>19330051920075</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="D14" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1371,24 +1413,162 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
+        <v>19330051920278</v>
+      </c>
+      <c r="B15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" t="s">
+        <v>65</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>19330051920284</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" t="s">
+        <v>66</v>
+      </c>
+      <c r="E16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>19330051920443</v>
+      </c>
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" t="s">
+        <v>67</v>
+      </c>
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>19330051920323</v>
+      </c>
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" t="s">
+        <v>68</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>19330051920332</v>
+      </c>
+      <c r="B19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
         <v>19330051920352</v>
       </c>
-      <c r="B15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15" t="s">
-        <v>57</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="B20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" t="s">
+        <v>70</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
         <v>12</v>
       </c>
-      <c r="G15">
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>19330051920353</v>
+      </c>
+      <c r="B21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" t="s">
+        <v>71</v>
+      </c>
+      <c r="E21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Domínguez Burgos Marioscar - Estadisticos 20212.xlsx
+++ b/docentes/Domínguez Burgos Marioscar - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="71">
   <si>
     <t>Mat</t>
   </si>
@@ -79,160 +79,157 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>XOLIO</t>
+  </si>
+  <si>
     <t>CHAVEZ</t>
   </si>
   <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>AJACTLE</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>MANZANET</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>GALVEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>MONTERO</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>TZOPITL</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>LINARES</t>
+  </si>
+  <si>
+    <t>ROQUE</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>ALTAMIRANO</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>MANZANET</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>GALVEZ</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>XOLIO</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>MONTERO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>LINARES</t>
-  </si>
-  <si>
-    <t>ROQUE</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>ALTAMIRANO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>ALEXIS ARMANDO</t>
+  </si>
+  <si>
+    <t>ALEXIS YAIR</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>ESDRAS ALAN</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>HERSON ELIAS</t>
   </si>
   <si>
     <t>EUSEBIO</t>
   </si>
   <si>
-    <t>JONATHAN</t>
-  </si>
-  <si>
     <t>ISAAC ALESSANDRO</t>
   </si>
   <si>
-    <t>ALEXIS YAIR</t>
-  </si>
-  <si>
     <t>IVAN</t>
   </si>
   <si>
-    <t>JOSUE YAMIN</t>
-  </si>
-  <si>
-    <t>ESDRAS ALAN</t>
+    <t>ELISA</t>
+  </si>
+  <si>
+    <t>ANDRES</t>
+  </si>
+  <si>
+    <t>CONCEPCION</t>
   </si>
   <si>
     <t>JADE EMILY</t>
   </si>
   <si>
-    <t>CARLO HUMBERTO</t>
-  </si>
-  <si>
-    <t>ALEXIS ARMANDO</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>ARTURO</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>CONCEPCION</t>
-  </si>
-  <si>
     <t>ASHLEY ZURELY</t>
   </si>
   <si>
     <t>ADRIAN</t>
   </si>
   <si>
+    <t>IGNACIO</t>
+  </si>
+  <si>
     <t>JESUS MANUEL</t>
   </si>
   <si>
     <t>ADAN</t>
   </si>
   <si>
-    <t>HERSON ELIAS</t>
+    <t>MERIELING YAMILETH</t>
   </si>
 </sst>
 </file>
@@ -633,19 +630,19 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G2">
-        <v>26.32</v>
+        <v>36.84</v>
       </c>
       <c r="H2">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -805,7 +802,7 @@
         <v>19</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -956,19 +953,19 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G2">
-        <v>26.32</v>
+        <v>36.84</v>
       </c>
       <c r="H2">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1114,16 +1111,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920045</v>
+        <v>19330051920058</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1137,16 +1134,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920057</v>
+        <v>19330051920067</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1160,16 +1157,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>18330051920022</v>
+        <v>19330051920068</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1183,22 +1180,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920067</v>
+        <v>19330051920273</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1206,22 +1203,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920074</v>
+        <v>19330051920330</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1229,22 +1226,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>18330051920078</v>
+        <v>19330051920330</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1252,22 +1249,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920273</v>
+        <v>19330051920353</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1275,91 +1272,91 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920286</v>
+        <v>19330051920045</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920308</v>
+        <v>18330051920022</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920308</v>
+        <v>19330051920074</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920058</v>
+        <v>19330051920269</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="D12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1367,22 +1364,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920068</v>
+        <v>19330051920278</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1390,22 +1387,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920075</v>
+        <v>19330051920284</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1413,16 +1410,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051920278</v>
+        <v>19330051920286</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -1436,16 +1433,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>19330051920284</v>
+        <v>19330051920443</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -1459,22 +1456,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>19330051920443</v>
+        <v>19330051920323</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1482,16 +1479,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>19330051920323</v>
+        <v>19330051920321</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C18" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D18" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1508,13 +1505,13 @@
         <v>19330051920332</v>
       </c>
       <c r="B19" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C19" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="D19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1531,13 +1528,13 @@
         <v>19330051920352</v>
       </c>
       <c r="B20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C20" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1551,22 +1548,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>19330051920353</v>
+        <v>19330051920394</v>
       </c>
       <c r="B21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G21">
         <v>1</v>

--- a/docentes/Domínguez Burgos Marioscar - Estadisticos 20212.xlsx
+++ b/docentes/Domínguez Burgos Marioscar - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="71">
   <si>
     <t>Mat</t>
   </si>
@@ -88,142 +88,142 @@
     <t>ARIAS</t>
   </si>
   <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>XOLIO</t>
+  </si>
+  <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>AJACTLE</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>XOLIO</t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>AJACTLE</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
     <t>MANZANET</t>
   </si>
   <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
     <t>GALVEZ</t>
   </si>
   <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
     <t>VILLA</t>
   </si>
   <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>MONTERO</t>
-  </si>
-  <si>
     <t>PACHECO</t>
   </si>
   <si>
     <t>BARRAGAN</t>
   </si>
   <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>LINARES</t>
+  </si>
+  <si>
+    <t>ROQUE</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>ALTAMIRANO</t>
+  </si>
+  <si>
     <t>TZOPITL</t>
   </si>
   <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>LINARES</t>
-  </si>
-  <si>
-    <t>ROQUE</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>ALTAMIRANO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>ORTIZ</t>
   </si>
   <si>
     <t>ALEXIS ARMANDO</t>
   </si>
   <si>
-    <t>ALEXIS YAIR</t>
-  </si>
-  <si>
     <t>EMMANUEL</t>
   </si>
   <si>
     <t>ESDRAS ALAN</t>
   </si>
   <si>
+    <t>IGNACIO</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>HERSON ELIAS</t>
+  </si>
+  <si>
+    <t>EUSEBIO</t>
+  </si>
+  <si>
+    <t>ISAAC ALESSANDRO</t>
+  </si>
+  <si>
+    <t>ELISA</t>
+  </si>
+  <si>
+    <t>ANDRES</t>
+  </si>
+  <si>
+    <t>CONCEPCION</t>
+  </si>
+  <si>
+    <t>JADE EMILY</t>
+  </si>
+  <si>
+    <t>KARLA</t>
+  </si>
+  <si>
+    <t>ASHLEY ZURELY</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
     <t>DIEGO</t>
-  </si>
-  <si>
-    <t>HERSON ELIAS</t>
-  </si>
-  <si>
-    <t>EUSEBIO</t>
-  </si>
-  <si>
-    <t>ISAAC ALESSANDRO</t>
-  </si>
-  <si>
-    <t>IVAN</t>
-  </si>
-  <si>
-    <t>ELISA</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>CONCEPCION</t>
-  </si>
-  <si>
-    <t>JADE EMILY</t>
-  </si>
-  <si>
-    <t>ASHLEY ZURELY</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>JESUS MANUEL</t>
   </si>
   <si>
     <t>ADAN</t>
@@ -630,10 +630,10 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F2">
         <v>7</v>
@@ -642,7 +642,7 @@
         <v>36.84</v>
       </c>
       <c r="H2">
-        <v>6.3</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -682,16 +682,16 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4">
         <v>10</v>
       </c>
       <c r="F4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G4">
-        <v>59.38</v>
+        <v>62.5</v>
       </c>
       <c r="H4">
         <v>7.2</v>
@@ -708,10 +708,10 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5">
         <v>22</v>
@@ -799,16 +799,19 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E2">
         <v>7</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>47.37</v>
+      </c>
+      <c r="H2">
+        <v>5.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -822,16 +825,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>70.97</v>
+      </c>
+      <c r="H3">
+        <v>7.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -845,16 +851,19 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="E4">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>59.38</v>
+      </c>
+      <c r="H4">
+        <v>7.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -868,16 +877,19 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="E5">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>65.63</v>
+      </c>
+      <c r="H5">
+        <v>7.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -891,16 +903,19 @@
         <v>33</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>72.73</v>
+      </c>
+      <c r="H6">
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -953,19 +968,19 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>36.84</v>
+        <v>47.37</v>
       </c>
       <c r="H2">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -982,16 +997,16 @@
         <v>1</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G3">
-        <v>77.42</v>
+        <v>70.97</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1005,19 +1020,19 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4">
         <v>10</v>
       </c>
       <c r="F4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G4">
-        <v>59.38</v>
+        <v>62.5</v>
       </c>
       <c r="H4">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1031,16 +1046,16 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G5">
-        <v>68.75</v>
+        <v>65.63</v>
       </c>
       <c r="H5">
         <v>7.4</v>
@@ -1069,7 +1084,7 @@
         <v>72.73</v>
       </c>
       <c r="H6">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -1079,7 +1094,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1117,10 +1132,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1134,16 +1149,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920067</v>
+        <v>19330051920068</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1157,22 +1172,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920068</v>
+        <v>19330051920273</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1180,22 +1195,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920273</v>
+        <v>19330051920321</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1203,7 +1218,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920330</v>
+        <v>19330051920321</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
@@ -1215,7 +1230,7 @@
         <v>56</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
         <v>12</v>
@@ -1226,16 +1241,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920330</v>
+        <v>19330051920338</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1252,13 +1267,13 @@
         <v>19330051920353</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1275,13 +1290,13 @@
         <v>19330051920045</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1298,13 +1313,13 @@
         <v>18330051920022</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1318,22 +1333,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920074</v>
+        <v>19330051920269</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1341,16 +1356,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920269</v>
+        <v>19330051920278</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -1364,16 +1379,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920278</v>
+        <v>19330051920284</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -1387,16 +1402,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920284</v>
+        <v>19330051920286</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -1410,16 +1425,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051920286</v>
+        <v>19330051920292</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -1436,13 +1451,13 @@
         <v>19330051920443</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -1459,13 +1474,13 @@
         <v>19330051920323</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1479,19 +1494,19 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>19330051920321</v>
+        <v>19330051920330</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C18" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="D18" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E18" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F18" t="s">
         <v>12</v>
@@ -1502,16 +1517,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>19330051920332</v>
+        <v>19330051920352</v>
       </c>
       <c r="B19" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="D19" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1525,47 +1540,24 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>19330051920352</v>
+        <v>19330051920394</v>
       </c>
       <c r="B20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C20" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D20" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E20" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>19330051920394</v>
-      </c>
-      <c r="B21" t="s">
-        <v>35</v>
-      </c>
-      <c r="C21" t="s">
-        <v>51</v>
-      </c>
-      <c r="D21" t="s">
-        <v>70</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G21">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Domínguez Burgos Marioscar - Estadisticos 20212.xlsx
+++ b/docentes/Domínguez Burgos Marioscar - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="68">
   <si>
     <t>Mat</t>
   </si>
@@ -85,27 +85,24 @@
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>XOLIO</t>
+  </si>
+  <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>AJACTLE</t>
+  </si>
+  <si>
     <t>ARIAS</t>
   </si>
   <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>XOLIO</t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>AJACTLE</t>
-  </si>
-  <si>
     <t>GARCIA</t>
   </si>
   <si>
@@ -133,27 +130,24 @@
     <t>PACHECO</t>
   </si>
   <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>BARRAGAN</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>LINARES</t>
   </si>
   <si>
@@ -184,25 +178,22 @@
     <t>EMMANUEL</t>
   </si>
   <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>HERSON ELIAS</t>
+  </si>
+  <si>
+    <t>EUSEBIO</t>
+  </si>
+  <si>
+    <t>ISAAC ALESSANDRO</t>
+  </si>
+  <si>
+    <t>ELISA</t>
+  </si>
+  <si>
     <t>ESDRAS ALAN</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
-    <t>HERSON ELIAS</t>
-  </si>
-  <si>
-    <t>EUSEBIO</t>
-  </si>
-  <si>
-    <t>ISAAC ALESSANDRO</t>
-  </si>
-  <si>
-    <t>ELISA</t>
   </si>
   <si>
     <t>ANDRES</t>
@@ -1094,7 +1085,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1132,10 +1123,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1155,10 +1146,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1172,22 +1163,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920273</v>
+        <v>19330051920338</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1195,16 +1186,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920321</v>
+        <v>19330051920353</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1218,91 +1209,91 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920321</v>
+        <v>19330051920045</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
         <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920338</v>
+        <v>18330051920022</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
         <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920353</v>
+        <v>19330051920269</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
         <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920045</v>
+        <v>19330051920273</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
         <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1310,22 +1301,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>18330051920022</v>
+        <v>19330051920278</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
         <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1333,16 +1324,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920269</v>
+        <v>19330051920284</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
         <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -1356,16 +1347,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920278</v>
+        <v>19330051920286</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
         <v>45</v>
       </c>
       <c r="D12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -1379,16 +1370,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920284</v>
+        <v>19330051920292</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
         <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -1402,16 +1393,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920286</v>
+        <v>19330051920443</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
         <v>47</v>
       </c>
       <c r="D14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -1425,22 +1416,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051920292</v>
+        <v>19330051920323</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
         <v>48</v>
       </c>
       <c r="D15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1448,22 +1439,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>19330051920443</v>
+        <v>19330051920330</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C16" t="s">
         <v>49</v>
       </c>
       <c r="D16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1471,16 +1462,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>19330051920323</v>
+        <v>19330051920352</v>
       </c>
       <c r="B17" t="s">
         <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1494,70 +1485,24 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>19330051920330</v>
+        <v>19330051920394</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D18" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>19330051920352</v>
-      </c>
-      <c r="B19" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" t="s">
-        <v>38</v>
-      </c>
-      <c r="D19" t="s">
-        <v>69</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>19330051920394</v>
-      </c>
-      <c r="B20" t="s">
-        <v>36</v>
-      </c>
-      <c r="C20" t="s">
-        <v>52</v>
-      </c>
-      <c r="D20" t="s">
-        <v>70</v>
-      </c>
-      <c r="E20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Domínguez Burgos Marioscar - Estadisticos 20212.xlsx
+++ b/docentes/Domínguez Burgos Marioscar - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="26">
   <si>
     <t>Mat</t>
   </si>
@@ -79,148 +79,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>XOLIO</t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>AJACTLE</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MANZANET</t>
-  </si>
-  <si>
     <t>RIVERA</t>
   </si>
   <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>GALVEZ</t>
-  </si>
-  <si>
     <t>VILLA</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
+    <t>SARMIENTO</t>
   </si>
   <si>
     <t>BARRAGAN</t>
   </si>
   <si>
-    <t>LINARES</t>
-  </si>
-  <si>
-    <t>ROQUE</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>ALTAMIRANO</t>
-  </si>
-  <si>
-    <t>TZOPITL</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>ALEXIS ARMANDO</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
-    <t>HERSON ELIAS</t>
-  </si>
-  <si>
-    <t>EUSEBIO</t>
-  </si>
-  <si>
-    <t>ISAAC ALESSANDRO</t>
-  </si>
-  <si>
-    <t>ELISA</t>
-  </si>
-  <si>
-    <t>ESDRAS ALAN</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>CONCEPCION</t>
-  </si>
-  <si>
-    <t>JADE EMILY</t>
-  </si>
-  <si>
-    <t>KARLA</t>
-  </si>
-  <si>
-    <t>ASHLEY ZURELY</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
+    <t>JOSUE YAMIN</t>
   </si>
   <si>
     <t>ADAN</t>
-  </si>
-  <si>
-    <t>MERIELING YAMILETH</t>
   </si>
 </sst>
 </file>
@@ -621,19 +495,19 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G2">
-        <v>36.84</v>
+        <v>42.11</v>
       </c>
       <c r="H2">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -647,10 +521,10 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3">
         <v>24</v>
@@ -659,7 +533,7 @@
         <v>77.42</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -673,10 +547,10 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F4">
         <v>20</v>
@@ -685,7 +559,7 @@
         <v>62.5</v>
       </c>
       <c r="H4">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -699,10 +573,10 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5">
         <v>22</v>
@@ -711,7 +585,7 @@
         <v>68.75</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -725,10 +599,10 @@
         <v>33</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F6">
         <v>24</v>
@@ -737,7 +611,7 @@
         <v>72.73</v>
       </c>
       <c r="H6">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -790,19 +664,19 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2">
-        <v>47.37</v>
+        <v>52.63</v>
       </c>
       <c r="H2">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -816,10 +690,10 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3">
         <v>22</v>
@@ -828,7 +702,7 @@
         <v>70.97</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -842,19 +716,19 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G4">
-        <v>59.38</v>
+        <v>62.5</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -868,10 +742,10 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5">
         <v>21</v>
@@ -880,7 +754,7 @@
         <v>65.63</v>
       </c>
       <c r="H5">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -894,10 +768,10 @@
         <v>33</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F6">
         <v>24</v>
@@ -906,7 +780,7 @@
         <v>72.73</v>
       </c>
       <c r="H6">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -959,16 +833,16 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G2">
-        <v>47.37</v>
+        <v>78.95</v>
       </c>
       <c r="H2">
         <v>6.1</v>
@@ -985,19 +859,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>70.97</v>
+        <v>93.55</v>
       </c>
       <c r="H3">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1011,19 +885,19 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G4">
-        <v>62.5</v>
+        <v>87.5</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1037,19 +911,19 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="G5">
-        <v>65.63</v>
+        <v>90.63</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1063,19 +937,19 @@
         <v>33</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G6">
-        <v>72.73</v>
+        <v>87.88</v>
       </c>
       <c r="H6">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1085,7 +959,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1117,16 +991,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920058</v>
+        <v>18330051920078</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" t="s">
         <v>24</v>
-      </c>
-      <c r="D2" t="s">
-        <v>51</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1140,369 +1014,24 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920068</v>
+        <v>19330051920352</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>19330051920338</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>19330051920353</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" t="s">
-        <v>54</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>19330051920045</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D6" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>18330051920022</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D7" t="s">
-        <v>56</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>19330051920269</v>
-      </c>
-      <c r="B8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D8" t="s">
-        <v>57</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>19330051920273</v>
-      </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" t="s">
-        <v>58</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>19330051920278</v>
-      </c>
-      <c r="B10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" t="s">
-        <v>59</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>19330051920284</v>
-      </c>
-      <c r="B11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" t="s">
-        <v>60</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>19330051920286</v>
-      </c>
-      <c r="B12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" t="s">
-        <v>61</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>19330051920292</v>
-      </c>
-      <c r="B13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13" t="s">
-        <v>62</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>19330051920443</v>
-      </c>
-      <c r="B14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14" t="s">
-        <v>63</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>11</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>19330051920323</v>
-      </c>
-      <c r="B15" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" t="s">
-        <v>48</v>
-      </c>
-      <c r="D15" t="s">
-        <v>64</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>19330051920330</v>
-      </c>
-      <c r="B16" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" t="s">
-        <v>49</v>
-      </c>
-      <c r="D16" t="s">
-        <v>65</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>19330051920352</v>
-      </c>
-      <c r="B17" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" t="s">
-        <v>42</v>
-      </c>
-      <c r="D17" t="s">
-        <v>66</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>19330051920394</v>
-      </c>
-      <c r="B18" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" t="s">
-        <v>50</v>
-      </c>
-      <c r="D18" t="s">
-        <v>67</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G18">
         <v>1</v>
       </c>
     </row>
